--- a/template/JaDE_현황판_시트템플릿.xlsx
+++ b/template/JaDE_현황판_시트템플릿.xlsx
@@ -11,11 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="마일스톤" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주간업무" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요건" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="녹화본" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출물" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이슈" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일정" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주간업무" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요건" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="녹화본" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출물" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이슈" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,6 +685,111 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>영향도</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>원인</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>상세</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>대응방안</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>기한</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>일정/선행조건</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>이슈 제목</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>상세 설명</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>대응 방안</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>JaDE PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>상시</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>영향도가 "높음"이면 붉은 태그로 표시되고 탭 배지에 건수가 올라갑니다.
+원인에 "자원"이 들어가면 붉은 태그, 그 외는 회색입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1917,6 +2023,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>시각</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>장소</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>참석자</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>회의</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>인사/조직 모듈 교육 및 추가개발 상세분석</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>고객사 본사</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>JaDE PM, 인사팀</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>방문·회의·교육 일정입니다. 일자와 제목만 있으면 되고 나머지 칸은 비워도 됩니다.
+구분은 방문 / 회의 / 교육 / 온라인 을 쓰면 색이 붙습니다. 다른 값도 그대로 표시됩니다.
+가장 가까운 예정 건이 화면 상단에 「다음 일정」 칩으로 뜹니다.
+이 시트를 지우면 방문·회의 탭도 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2043,7 +2252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2132,7 +2341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2227,7 +2436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2335,109 +2544,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>영향도</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>원인</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>상세</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>대응방안</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>담당</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>기한</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>일정/선행조건</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>이슈 제목</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>상세 설명</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>대응 방안</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>JaDE PM</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>상시</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>영향도가 "높음"이면 붉은 태그로 표시되고 탭 배지에 건수가 올라갑니다.
-원인에 "자원"이 들어가면 붉은 태그, 그 외는 회색입니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/template/JaDE_현황판_시트템플릿.xlsx
+++ b/template/JaDE_현황판_시트템플릿.xlsx
@@ -2258,7 +2258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2267,6 +2267,8 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2300,6 +2302,16 @@
           <t>상태</t>
         </is>
       </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>설계검토서</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>개발완료보고서</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2328,11 +2340,17 @@
           <t>대기</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://…</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>추가개발 요건 대장입니다. 비워두면 추가개발 탭에서 이 표가 빠집니다.</t>
+          <t>추가개발 요건 대장입니다. 비워두면 추가개발 탭에서 이 표가 빠집니다. 설계검토서·개발완료보고서 칸에 요건별 URL 을 적으면 줄마다 「열기」 버튼이 생깁니다.</t>
         </is>
       </c>
     </row>
